--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/SAN LORENZO 2.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/SAN LORENZO 2.xlsx
@@ -269,487 +269,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="876300" cy="895350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image8.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="733425" cy="695325"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image13.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="533400" cy="704850"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image9.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="304800" cy="514350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="image2.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="533400" cy="676275"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="image12.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="428625" cy="628650"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="image5.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="352425" cy="504825"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="image14.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="523875" cy="485775"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="image3.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="304800" cy="457200"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="image7.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="342900" cy="457200"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="image4.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="561975" cy="600075"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="image6.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="352425" cy="561975"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="image11.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="466725" cy="504825"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="image10.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="438150" cy="466725"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="image1.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
